--- a/08-ai-governance-eu-ai-act-iso42001/08-ai-governance-assessment.xlsx
+++ b/08-ai-governance-eu-ai-act-iso42001/08-ai-governance-assessment.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Approving authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer</t>
+    <t xml:space="preserve">Jerry Gold, Chief Executive Officer</t>
   </si>
   <si>
     <t xml:space="preserve">Status</t>
